--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_event.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_event.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="event" sheetId="1" r:id="rId3"/>
+    <sheet name="event" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -156,7 +156,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Ha! Ha! Ha! Such pitiable lamentations!</t>
@@ -255,37 +255,6 @@
   <si>
     <t xml:space="preserve">1,white</t>
   </si>
-  <si>
-    <t xml:space="preserve">「…剑」「我的剑…」
-哈哈哈，何等不甘的悲叹！</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">凡人们啊
-不，虫豸们啊
-你们的剑，会永远侍奉于我。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对神明刀刃相向的蠢货就是你吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我一直在看着，这一切的始末。
-灵魂们被解放时发出的悲鸣
-真是相当有趣的旋律。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好啊，虫子。我来当你的对手。
-来与这把剑一起起舞吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不、不可能…我竟被这虫豸…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡人啊，你给我记住了。
-总有一天，我定会将剑夺回！</t>
-  </si>
 </sst>
 </file>
 
@@ -306,32 +275,32 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -376,7 +345,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -385,78 +354,78 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -470,13 +439,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -652,24 +621,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW235"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.33" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.12" style="2" customWidth="1"/>
-    <col min="10" max="10" width="62.98" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="62.98"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,13 +673,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -718,7 +687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
@@ -726,7 +695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -734,7 +703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
@@ -742,7 +711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
@@ -750,7 +719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -758,7 +727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
@@ -766,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
@@ -774,7 +743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
@@ -782,7 +751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
@@ -790,7 +759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
@@ -798,7 +767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
@@ -806,7 +775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -814,7 +783,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
         <v>13</v>
       </c>
@@ -822,7 +791,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
@@ -830,7 +799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>13</v>
       </c>
@@ -838,7 +807,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>13</v>
       </c>
@@ -846,7 +815,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
@@ -854,7 +823,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
@@ -862,7 +831,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
@@ -870,17 +839,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1135,15 +1104,15 @@
       <c r="IV28" s="1"/>
       <c r="IW28" s="1"/>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="1" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="30" s="6" customFormat="1" ht="23.85">
+    <row r="30" s="6" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1151,7 +1120,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="1">
+      <c r="H30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -1160,9 +1129,7 @@
       <c r="J30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -1410,8 +1377,8 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" ht="35.05">
-      <c r="H31" s="1">
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -1420,11 +1387,8 @@
       <c r="J31" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K31" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="32" s="6" customFormat="1" ht="12.8">
+    <row r="32" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1683,15 +1647,15 @@
       <c r="IV32" s="1"/>
       <c r="IW32" s="1"/>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="1" t="s">
         <v>42</v>
       </c>
@@ -1699,7 +1663,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="1" t="s">
         <v>44</v>
       </c>
@@ -1707,7 +1671,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="1" t="s">
         <v>46</v>
       </c>
@@ -1715,7 +1679,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="1" t="s">
         <v>48</v>
       </c>
@@ -1723,7 +1687,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="1" t="s">
         <v>49</v>
       </c>
@@ -1731,28 +1695,28 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="41" ht="13.8">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="1" t="n">
         <v>101</v>
       </c>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" ht="13.8">
-      <c r="H42" s="1">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I42" s="9" t="s">
@@ -1761,12 +1725,9 @@
       <c r="J42" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K42" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="43" ht="37.3">
-      <c r="H43" s="1">
+    <row r="43" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I43" s="9" t="s">
@@ -1775,12 +1736,9 @@
       <c r="J43" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="K43" t="s">
-        <v>71</v>
-      </c>
     </row>
-    <row r="44" ht="23.85">
-      <c r="H44" s="1">
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I44" s="4" t="s">
@@ -1789,48 +1747,45 @@
       <c r="J44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K44" t="s">
-        <v>72</v>
-      </c>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="s">
         <v>60</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="1" t="s">
         <v>35</v>
       </c>
@@ -2085,7 +2040,7 @@
       <c r="IV51" s="1"/>
       <c r="IW51" s="1"/>
     </row>
-    <row r="52" s="6" customFormat="1" ht="13.8">
+    <row r="52" s="6" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2093,7 +2048,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="1">
+      <c r="H52" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I52" s="4" t="s">
@@ -2102,9 +2057,7 @@
       <c r="J52" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
@@ -2352,8 +2305,8 @@
       <c r="IV52" s="1"/>
       <c r="IW52" s="1"/>
     </row>
-    <row r="53" ht="23.85">
-      <c r="H53" s="1">
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I53" s="4" t="s">
@@ -2362,11 +2315,8 @@
       <c r="J53" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K53" t="s">
-        <v>74</v>
-      </c>
     </row>
-    <row r="54" s="6" customFormat="1" ht="12.8">
+    <row r="54" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2625,7 +2575,7 @@
       <c r="IV54" s="1"/>
       <c r="IW54" s="1"/>
     </row>
-    <row r="55" ht="12.8">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D55" s="1" t="s">
         <v>44</v>
       </c>
@@ -2633,7 +2583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" ht="12.8">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2641,34 +2591,34 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" ht="13.8">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="s">
         <v>60</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
     </row>
-    <row r="61" s="6" customFormat="1" ht="12.8">
+    <row r="61" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2927,7 +2877,7 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" ht="12.8">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -3176,7 +3126,7 @@
       <c r="IV62" s="1"/>
       <c r="IW62" s="1"/>
     </row>
-    <row r="64" ht="12.8">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -3425,7 +3375,7 @@
       <c r="IV64" s="1"/>
       <c r="IW64" s="1"/>
     </row>
-    <row r="68" s="11" customFormat="1" ht="12.8">
+    <row r="68" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3684,7 +3634,7 @@
       <c r="IV68" s="1"/>
       <c r="IW68" s="1"/>
     </row>
-    <row r="82" s="11" customFormat="1" ht="12.8">
+    <row r="82" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3943,7 +3893,7 @@
       <c r="IV82" s="1"/>
       <c r="IW82" s="1"/>
     </row>
-    <row r="83" s="11" customFormat="1" ht="12.8">
+    <row r="83" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4202,7 +4152,7 @@
       <c r="IV83" s="1"/>
       <c r="IW83" s="1"/>
     </row>
-    <row r="96" s="11" customFormat="1" ht="12.8">
+    <row r="96" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4461,7 +4411,7 @@
       <c r="IV96" s="1"/>
       <c r="IW96" s="1"/>
     </row>
-    <row r="102" s="6" customFormat="1" ht="12.8">
+    <row r="102" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4720,7 +4670,7 @@
       <c r="IV102" s="1"/>
       <c r="IW102" s="1"/>
     </row>
-    <row r="109" s="6" customFormat="1" ht="12.8">
+    <row r="109" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4979,7 +4929,7 @@
       <c r="IV109" s="1"/>
       <c r="IW109" s="1"/>
     </row>
-    <row r="133" s="6" customFormat="1" ht="12.8">
+    <row r="133" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5238,7 +5188,7 @@
       <c r="IV133" s="1"/>
       <c r="IW133" s="1"/>
     </row>
-    <row r="144" s="6" customFormat="1" ht="12.8">
+    <row r="144" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5497,7 +5447,7 @@
       <c r="IV144" s="1"/>
       <c r="IW144" s="1"/>
     </row>
-    <row r="150" s="11" customFormat="1" ht="12.8">
+    <row r="150" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5756,7 +5706,7 @@
       <c r="IV150" s="1"/>
       <c r="IW150" s="1"/>
     </row>
-    <row r="151" s="11" customFormat="1" ht="12.8">
+    <row r="151" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -6015,7 +5965,7 @@
       <c r="IV151" s="1"/>
       <c r="IW151" s="1"/>
     </row>
-    <row r="162" s="11" customFormat="1" ht="12.8">
+    <row r="162" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6274,7 +6224,7 @@
       <c r="IV162" s="1"/>
       <c r="IW162" s="1"/>
     </row>
-    <row r="207" s="11" customFormat="1" ht="12.8">
+    <row r="207" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6533,7 +6483,7 @@
       <c r="IV207" s="1"/>
       <c r="IW207" s="1"/>
     </row>
-    <row r="211" s="6" customFormat="1" ht="12.8">
+    <row r="211" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6792,7 +6742,7 @@
       <c r="IV211" s="1"/>
       <c r="IW211" s="1"/>
     </row>
-    <row r="212" s="11" customFormat="1" ht="12.8">
+    <row r="212" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7051,7 +7001,7 @@
       <c r="IV212" s="1"/>
       <c r="IW212" s="1"/>
     </row>
-    <row r="225" s="11" customFormat="1" ht="12.8">
+    <row r="225" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7310,7 +7260,7 @@
       <c r="IV225" s="1"/>
       <c r="IW225" s="1"/>
     </row>
-    <row r="226" s="11" customFormat="1" ht="12.8">
+    <row r="226" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7569,7 +7519,7 @@
       <c r="IV226" s="1"/>
       <c r="IW226" s="1"/>
     </row>
-    <row r="235" s="6" customFormat="1" ht="12.8">
+    <row r="235" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7830,12 +7780,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_event.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_event.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="event" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="event" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -156,7 +156,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Ha! Ha! Ha! Such pitiable lamentations!</t>
@@ -255,6 +255,37 @@
   <si>
     <t xml:space="preserve">1,white</t>
   </si>
+  <si>
+    <t xml:space="preserve">「…剑」「我的剑…」
+哈哈哈，何等不甘的悲叹！</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">凡人们啊
+不，虫豸们啊
+你们的剑，会永远侍奉于我。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对神明刀刃相向的蠢货就是你吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我一直在看着，这一切的始末。
+灵魂们被解放时发出的悲鸣
+真是相当有趣的旋律。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好啊，虫子。我来当你的对手。
+来与这把剑一起起舞吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不、不可能…我竟被这虫豸…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凡人啊，你给我记住了。
+总有一天，我定会将剑夺回！</t>
+  </si>
 </sst>
 </file>
 
@@ -275,32 +306,32 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -345,7 +376,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -354,78 +385,78 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -439,13 +470,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -621,24 +652,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IW235"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="62.98"/>
+    <col min="1" max="1" width="19.33" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="62.12" style="2" customWidth="1"/>
+    <col min="10" max="10" width="62.98" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,13 +704,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -687,7 +718,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
@@ -695,7 +726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -703,7 +734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
@@ -711,7 +742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
@@ -719,7 +750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -727,7 +758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
@@ -735,7 +766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
@@ -743,7 +774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
@@ -751,7 +782,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
@@ -759,7 +790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
@@ -767,7 +798,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
@@ -775,7 +806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -783,7 +814,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="D18" s="1" t="s">
         <v>13</v>
       </c>
@@ -791,7 +822,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
@@ -799,7 +830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>13</v>
       </c>
@@ -807,7 +838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>13</v>
       </c>
@@ -815,7 +846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
@@ -823,7 +854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
@@ -831,7 +862,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
@@ -839,17 +870,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1104,15 +1135,15 @@
       <c r="IV28" s="1"/>
       <c r="IW28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="D29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="30" s="6" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="6" customFormat="1" ht="23.85">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1120,7 +1151,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -1129,7 +1160,9 @@
       <c r="J30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -1377,8 +1410,8 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H31" s="1" t="n">
+    <row r="31" ht="35.05">
+      <c r="H31" s="1">
         <v>2</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -1387,8 +1420,11 @@
       <c r="J31" s="4" t="s">
         <v>41</v>
       </c>
+      <c r="K31" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="32" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="6" customFormat="1" ht="12.8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1647,15 +1683,15 @@
       <c r="IV32" s="1"/>
       <c r="IW32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="D33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="D34" s="1" t="s">
         <v>42</v>
       </c>
@@ -1663,7 +1699,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="D35" s="1" t="s">
         <v>44</v>
       </c>
@@ -1671,7 +1707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="D36" s="1" t="s">
         <v>46</v>
       </c>
@@ -1679,7 +1715,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="D37" s="1" t="s">
         <v>48</v>
       </c>
@@ -1687,7 +1723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="D38" s="1" t="s">
         <v>49</v>
       </c>
@@ -1695,28 +1731,28 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="D40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="13.8">
       <c r="C41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="1">
         <v>101</v>
       </c>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H42" s="1" t="n">
+    <row r="42" ht="13.8">
+      <c r="H42" s="1">
         <v>3</v>
       </c>
       <c r="I42" s="9" t="s">
@@ -1725,9 +1761,12 @@
       <c r="J42" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="K42" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="43" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H43" s="1" t="n">
+    <row r="43" ht="37.3">
+      <c r="H43" s="1">
         <v>4</v>
       </c>
       <c r="I43" s="9" t="s">
@@ -1736,9 +1775,12 @@
       <c r="J43" s="4" t="s">
         <v>55</v>
       </c>
+      <c r="K43" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H44" s="1" t="n">
+    <row r="44" ht="23.85">
+      <c r="H44" s="1">
         <v>5</v>
       </c>
       <c r="I44" s="4" t="s">
@@ -1747,45 +1789,48 @@
       <c r="J44" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="K44" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="D45" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="D46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="D47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="B48" s="1" t="s">
         <v>60</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="D51" s="1" t="s">
         <v>35</v>
       </c>
@@ -2040,7 +2085,7 @@
       <c r="IV51" s="1"/>
       <c r="IW51" s="1"/>
     </row>
-    <row r="52" s="6" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="6" customFormat="1" ht="13.8">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2048,7 +2093,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="1" t="n">
+      <c r="H52" s="1">
         <v>6</v>
       </c>
       <c r="I52" s="4" t="s">
@@ -2057,7 +2102,9 @@
       <c r="J52" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="K52" s="1"/>
+      <c r="K52" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
@@ -2305,8 +2352,8 @@
       <c r="IV52" s="1"/>
       <c r="IW52" s="1"/>
     </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H53" s="1" t="n">
+    <row r="53" ht="23.85">
+      <c r="H53" s="1">
         <v>7</v>
       </c>
       <c r="I53" s="4" t="s">
@@ -2315,8 +2362,11 @@
       <c r="J53" s="4" t="s">
         <v>65</v>
       </c>
+      <c r="K53" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="54" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" s="6" customFormat="1" ht="12.8">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2575,7 +2625,7 @@
       <c r="IV54" s="1"/>
       <c r="IW54" s="1"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="12.8">
       <c r="D55" s="1" t="s">
         <v>44</v>
       </c>
@@ -2583,7 +2633,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="12.8">
       <c r="D56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2591,34 +2641,34 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="13.8">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="1">
         <v>28</v>
       </c>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="D59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="B60" s="1" t="s">
         <v>60</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
     </row>
-    <row r="61" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="6" customFormat="1" ht="12.8">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2877,7 +2927,7 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="12.8">
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -3126,7 +3176,7 @@
       <c r="IV62" s="1"/>
       <c r="IW62" s="1"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.8">
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -3375,7 +3425,7 @@
       <c r="IV64" s="1"/>
       <c r="IW64" s="1"/>
     </row>
-    <row r="68" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="11" customFormat="1" ht="12.8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3634,7 +3684,7 @@
       <c r="IV68" s="1"/>
       <c r="IW68" s="1"/>
     </row>
-    <row r="82" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="11" customFormat="1" ht="12.8">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3893,7 +3943,7 @@
       <c r="IV82" s="1"/>
       <c r="IW82" s="1"/>
     </row>
-    <row r="83" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" s="11" customFormat="1" ht="12.8">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4152,7 +4202,7 @@
       <c r="IV83" s="1"/>
       <c r="IW83" s="1"/>
     </row>
-    <row r="96" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" s="11" customFormat="1" ht="12.8">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4411,7 +4461,7 @@
       <c r="IV96" s="1"/>
       <c r="IW96" s="1"/>
     </row>
-    <row r="102" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" s="6" customFormat="1" ht="12.8">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4670,7 +4720,7 @@
       <c r="IV102" s="1"/>
       <c r="IW102" s="1"/>
     </row>
-    <row r="109" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" s="6" customFormat="1" ht="12.8">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4929,7 +4979,7 @@
       <c r="IV109" s="1"/>
       <c r="IW109" s="1"/>
     </row>
-    <row r="133" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" s="6" customFormat="1" ht="12.8">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5188,7 +5238,7 @@
       <c r="IV133" s="1"/>
       <c r="IW133" s="1"/>
     </row>
-    <row r="144" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" s="6" customFormat="1" ht="12.8">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5447,7 +5497,7 @@
       <c r="IV144" s="1"/>
       <c r="IW144" s="1"/>
     </row>
-    <row r="150" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="11" customFormat="1" ht="12.8">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5706,7 +5756,7 @@
       <c r="IV150" s="1"/>
       <c r="IW150" s="1"/>
     </row>
-    <row r="151" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" s="11" customFormat="1" ht="12.8">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5965,7 +6015,7 @@
       <c r="IV151" s="1"/>
       <c r="IW151" s="1"/>
     </row>
-    <row r="162" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" s="11" customFormat="1" ht="12.8">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6224,7 +6274,7 @@
       <c r="IV162" s="1"/>
       <c r="IW162" s="1"/>
     </row>
-    <row r="207" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" s="11" customFormat="1" ht="12.8">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6483,7 +6533,7 @@
       <c r="IV207" s="1"/>
       <c r="IW207" s="1"/>
     </row>
-    <row r="211" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="6" customFormat="1" ht="12.8">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6742,7 +6792,7 @@
       <c r="IV211" s="1"/>
       <c r="IW211" s="1"/>
     </row>
-    <row r="212" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" s="11" customFormat="1" ht="12.8">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7001,7 +7051,7 @@
       <c r="IV212" s="1"/>
       <c r="IW212" s="1"/>
     </row>
-    <row r="225" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" s="11" customFormat="1" ht="12.8">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7260,7 +7310,7 @@
       <c r="IV225" s="1"/>
       <c r="IW225" s="1"/>
     </row>
-    <row r="226" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" s="11" customFormat="1" ht="12.8">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7519,7 +7569,7 @@
       <c r="IV226" s="1"/>
       <c r="IW226" s="1"/>
     </row>
-    <row r="235" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" s="6" customFormat="1" ht="12.8">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7780,12 +7830,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
